--- a/MaPeer Appointments.xlsx
+++ b/MaPeer Appointments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nwafo\Training\Backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44405F5-31CB-4822-89AC-F7534D76DC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05EC31D-38AD-4C74-B527-358FFE082E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{5FECE9FE-F25A-4E26-840F-A67091CF8745}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5441" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5441" uniqueCount="1037">
   <si>
     <t>Model Primary Health Care Uyo</t>
   </si>
@@ -2968,9 +2968,6 @@
   </si>
   <si>
     <t>Federal Housing Estate Uyo</t>
-  </si>
-  <si>
-    <t>completed</t>
   </si>
   <si>
     <t>2a7b3c9d8e5f1a2b3c4d5e6f</t>
@@ -3872,7 +3869,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6D12FD30-788E-4475-9A44-02CDE798DCD4}" name="Table1" displayName="Table1" ref="A1:L547" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="14">
-  <autoFilter ref="A1:L547" xr:uid="{6D12FD30-788E-4475-9A44-02CDE798DCD4}"/>
+  <autoFilter ref="A1:L547" xr:uid="{6D12FD30-788E-4475-9A44-02CDE798DCD4}">
+    <filterColumn colId="10">
+      <filters>
+        <dateGroupItem year="2026" month="5" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{EEE8160D-A081-4188-A0F1-E7162CBF6D16}" name="S/N" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{6D4CFB18-B097-42B5-9F40-62FC0C8870FF}" name="USER_NAME" dataDxfId="12"/>
@@ -4244,7 +4247,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>99</v>
       </c>
@@ -4282,7 +4285,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>102</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>105</v>
       </c>
@@ -4358,7 +4361,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>108</v>
       </c>
@@ -4396,7 +4399,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>111</v>
       </c>
@@ -4434,7 +4437,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>114</v>
       </c>
@@ -4472,7 +4475,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>117</v>
       </c>
@@ -4510,7 +4513,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>120</v>
       </c>
@@ -4546,7 +4549,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>122</v>
       </c>
@@ -4584,7 +4587,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>125</v>
       </c>
@@ -4622,7 +4625,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>128</v>
       </c>
@@ -4660,7 +4663,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>130</v>
       </c>
@@ -4698,7 +4701,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>133</v>
       </c>
@@ -4736,7 +4739,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>136</v>
       </c>
@@ -4774,7 +4777,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>139</v>
       </c>
@@ -4812,7 +4815,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>142</v>
       </c>
@@ -4850,7 +4853,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>145</v>
       </c>
@@ -4888,7 +4891,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>148</v>
       </c>
@@ -4926,7 +4929,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>151</v>
       </c>
@@ -4964,7 +4967,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>154</v>
       </c>
@@ -5002,7 +5005,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>157</v>
       </c>
@@ -5038,7 +5041,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>160</v>
       </c>
@@ -5112,7 +5115,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>166</v>
       </c>
@@ -5150,7 +5153,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>169</v>
       </c>
@@ -5188,7 +5191,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>172</v>
       </c>
@@ -5226,7 +5229,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>175</v>
       </c>
@@ -5264,7 +5267,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>178</v>
       </c>
@@ -5302,7 +5305,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>181</v>
       </c>
@@ -5340,7 +5343,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>183</v>
       </c>
@@ -5378,7 +5381,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>186</v>
       </c>
@@ -5414,7 +5417,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>189</v>
       </c>
@@ -5452,7 +5455,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>192</v>
       </c>
@@ -5490,7 +5493,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>195</v>
       </c>
@@ -5528,7 +5531,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>197</v>
       </c>
@@ -5566,7 +5569,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>200</v>
       </c>
@@ -5604,7 +5607,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>203</v>
       </c>
@@ -5642,7 +5645,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>206</v>
       </c>
@@ -5680,7 +5683,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>209</v>
       </c>
@@ -5718,7 +5721,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>212</v>
       </c>
@@ -5756,7 +5759,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>215</v>
       </c>
@@ -5794,7 +5797,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>218</v>
       </c>
@@ -5832,7 +5835,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>221</v>
       </c>
@@ -5870,7 +5873,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>224</v>
       </c>
@@ -5906,7 +5909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>227</v>
       </c>
@@ -5976,11 +5979,11 @@
       <c r="K47" s="15">
         <v>46147</v>
       </c>
-      <c r="L47" s="18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="L47" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>233</v>
       </c>
@@ -6018,7 +6021,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>236</v>
       </c>
@@ -6056,7 +6059,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>238</v>
       </c>
@@ -6094,7 +6097,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>241</v>
       </c>
@@ -6132,7 +6135,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>244</v>
       </c>
@@ -6170,7 +6173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>247</v>
       </c>
@@ -6208,7 +6211,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>250</v>
       </c>
@@ -6246,7 +6249,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>253</v>
       </c>
@@ -6282,7 +6285,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>256</v>
       </c>
@@ -6320,7 +6323,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
         <v>259</v>
       </c>
@@ -6358,7 +6361,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>262</v>
       </c>
@@ -6396,7 +6399,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>265</v>
       </c>
@@ -6434,7 +6437,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>268</v>
       </c>
@@ -6472,7 +6475,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
         <v>271</v>
       </c>
@@ -6510,7 +6513,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>274</v>
       </c>
@@ -6548,7 +6551,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
         <v>276</v>
       </c>
@@ -6586,7 +6589,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>279</v>
       </c>
@@ -6624,7 +6627,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
         <v>282</v>
       </c>
@@ -6662,7 +6665,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>285</v>
       </c>
@@ -6700,7 +6703,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>288</v>
       </c>
@@ -6738,7 +6741,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>291</v>
       </c>
@@ -6774,7 +6777,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
         <v>294</v>
       </c>
@@ -6848,7 +6851,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>300</v>
       </c>
@@ -6886,7 +6889,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>303</v>
       </c>
@@ -6924,7 +6927,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
         <v>306</v>
       </c>
@@ -6962,7 +6965,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>309</v>
       </c>
@@ -7000,7 +7003,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
         <v>312</v>
       </c>
@@ -7038,7 +7041,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>315</v>
       </c>
@@ -7076,7 +7079,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
         <v>318</v>
       </c>
@@ -7114,7 +7117,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
         <v>321</v>
       </c>
@@ -7150,7 +7153,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
         <v>324</v>
       </c>
@@ -7188,7 +7191,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
         <v>327</v>
       </c>
@@ -7226,7 +7229,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>330</v>
       </c>
@@ -7264,7 +7267,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>333</v>
       </c>
@@ -7302,7 +7305,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
         <v>336</v>
       </c>
@@ -7340,7 +7343,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
         <v>339</v>
       </c>
@@ -7378,7 +7381,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
         <v>342</v>
       </c>
@@ -7416,7 +7419,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
         <v>345</v>
       </c>
@@ -7454,7 +7457,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
         <v>348</v>
       </c>
@@ -7492,7 +7495,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
         <v>351</v>
       </c>
@@ -7530,7 +7533,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
         <v>354</v>
       </c>
@@ -7568,7 +7571,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
         <v>357</v>
       </c>
@@ -7606,7 +7609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
         <v>360</v>
       </c>
@@ -7642,7 +7645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
         <v>363</v>
       </c>
@@ -7712,11 +7715,11 @@
       <c r="K93" s="24">
         <v>46146</v>
       </c>
-      <c r="L93" s="18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L93" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
         <v>369</v>
       </c>
@@ -7754,7 +7757,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>372</v>
       </c>
@@ -7792,7 +7795,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
         <v>375</v>
       </c>
@@ -7830,7 +7833,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
         <v>378</v>
       </c>
@@ -7868,7 +7871,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
         <v>381</v>
       </c>
@@ -7906,7 +7909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
         <v>384</v>
       </c>
@@ -7944,7 +7947,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
         <v>387</v>
       </c>
@@ -7982,7 +7985,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
         <v>390</v>
       </c>
@@ -8058,7 +8061,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
         <v>395</v>
       </c>
@@ -8096,7 +8099,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
         <v>398</v>
       </c>
@@ -8168,11 +8171,11 @@
       <c r="K105" s="24">
         <v>46150</v>
       </c>
-      <c r="L105" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L105" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
         <v>404</v>
       </c>
@@ -8244,11 +8247,11 @@
       <c r="K107" s="27">
         <v>46146</v>
       </c>
-      <c r="L107" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L107" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
         <v>410</v>
       </c>
@@ -8286,7 +8289,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
         <v>413</v>
       </c>
@@ -8324,7 +8327,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
         <v>416</v>
       </c>
@@ -8362,7 +8365,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
         <v>419</v>
       </c>
@@ -8400,7 +8403,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
         <v>422</v>
       </c>
@@ -8438,7 +8441,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
         <v>422</v>
       </c>
@@ -8476,7 +8479,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
         <v>422</v>
       </c>
@@ -8514,7 +8517,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
         <v>422</v>
       </c>
@@ -8552,7 +8555,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
         <v>422</v>
       </c>
@@ -8590,7 +8593,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
         <v>422</v>
       </c>
@@ -8628,7 +8631,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
         <v>422</v>
       </c>
@@ -8666,7 +8669,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
         <v>422</v>
       </c>
@@ -8704,7 +8707,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="8" t="s">
         <v>422</v>
       </c>
@@ -8742,7 +8745,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
         <v>422</v>
       </c>
@@ -8780,7 +8783,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
         <v>422</v>
       </c>
@@ -8818,7 +8821,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
         <v>422</v>
       </c>
@@ -8856,7 +8859,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
         <v>422</v>
       </c>
@@ -8894,7 +8897,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
         <v>422</v>
       </c>
@@ -8932,7 +8935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="8" t="s">
         <v>422</v>
       </c>
@@ -8970,7 +8973,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
         <v>422</v>
       </c>
@@ -9008,7 +9011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
         <v>422</v>
       </c>
@@ -9046,7 +9049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
         <v>422</v>
       </c>
@@ -9084,7 +9087,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
         <v>422</v>
       </c>
@@ -9122,7 +9125,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
         <v>422</v>
       </c>
@@ -9160,7 +9163,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
         <v>422</v>
       </c>
@@ -9198,7 +9201,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
         <v>422</v>
       </c>
@@ -9236,7 +9239,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="8" t="s">
         <v>422</v>
       </c>
@@ -9274,7 +9277,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
         <v>422</v>
       </c>
@@ -9312,7 +9315,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="8" t="s">
         <v>422</v>
       </c>
@@ -9350,7 +9353,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
         <v>422</v>
       </c>
@@ -9388,7 +9391,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
         <v>422</v>
       </c>
@@ -9426,7 +9429,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
         <v>422</v>
       </c>
@@ -9464,7 +9467,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="8" t="s">
         <v>422</v>
       </c>
@@ -9502,7 +9505,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
         <v>422</v>
       </c>
@@ -9540,7 +9543,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="8" t="s">
         <v>422</v>
       </c>
@@ -9578,7 +9581,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
         <v>422</v>
       </c>
@@ -9616,7 +9619,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="8" t="s">
         <v>422</v>
       </c>
@@ -9654,7 +9657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
         <v>422</v>
       </c>
@@ -9692,7 +9695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="8" t="s">
         <v>422</v>
       </c>
@@ -9730,7 +9733,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
         <v>422</v>
       </c>
@@ -9768,7 +9771,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
         <v>422</v>
       </c>
@@ -9806,7 +9809,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
         <v>422</v>
       </c>
@@ -9844,7 +9847,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="8" t="s">
         <v>422</v>
       </c>
@@ -9882,7 +9885,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
         <v>422</v>
       </c>
@@ -9920,7 +9923,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="8" t="s">
         <v>422</v>
       </c>
@@ -9958,7 +9961,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
         <v>422</v>
       </c>
@@ -9996,7 +9999,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="8" t="s">
         <v>422</v>
       </c>
@@ -10034,7 +10037,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
         <v>422</v>
       </c>
@@ -10072,7 +10075,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="8" t="s">
         <v>422</v>
       </c>
@@ -10110,7 +10113,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="12" t="s">
         <v>422</v>
       </c>
@@ -10148,7 +10151,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="8" t="s">
         <v>422</v>
       </c>
@@ -10186,7 +10189,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
         <v>422</v>
       </c>
@@ -10224,7 +10227,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="8" t="s">
         <v>422</v>
       </c>
@@ -10262,7 +10265,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
         <v>422</v>
       </c>
@@ -10300,7 +10303,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="8" t="s">
         <v>422</v>
       </c>
@@ -10338,7 +10341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
         <v>422</v>
       </c>
@@ -10376,7 +10379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="8" t="s">
         <v>422</v>
       </c>
@@ -10414,7 +10417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
         <v>422</v>
       </c>
@@ -10452,7 +10455,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
         <v>422</v>
       </c>
@@ -10490,7 +10493,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
         <v>422</v>
       </c>
@@ -10528,7 +10531,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
         <v>422</v>
       </c>
@@ -10566,7 +10569,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
         <v>422</v>
       </c>
@@ -10604,7 +10607,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
         <v>422</v>
       </c>
@@ -10642,7 +10645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
         <v>422</v>
       </c>
@@ -10680,7 +10683,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
         <v>422</v>
       </c>
@@ -10718,7 +10721,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
         <v>422</v>
       </c>
@@ -10756,7 +10759,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
         <v>422</v>
       </c>
@@ -10794,7 +10797,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
         <v>422</v>
       </c>
@@ -10832,7 +10835,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
         <v>422</v>
       </c>
@@ -10870,7 +10873,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="12" t="s">
         <v>422</v>
       </c>
@@ -10908,7 +10911,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
         <v>422</v>
       </c>
@@ -10946,7 +10949,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="12" t="s">
         <v>422</v>
       </c>
@@ -10984,7 +10987,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
         <v>422</v>
       </c>
@@ -11022,7 +11025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
         <v>422</v>
       </c>
@@ -11060,7 +11063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
         <v>422</v>
       </c>
@@ -11098,7 +11101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12" t="s">
         <v>422</v>
       </c>
@@ -11136,7 +11139,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
         <v>422</v>
       </c>
@@ -11174,7 +11177,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
         <v>422</v>
       </c>
@@ -11212,7 +11215,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
         <v>422</v>
       </c>
@@ -11250,7 +11253,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
         <v>422</v>
       </c>
@@ -11288,7 +11291,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
         <v>422</v>
       </c>
@@ -11326,7 +11329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12" t="s">
         <v>422</v>
       </c>
@@ -11364,7 +11367,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
         <v>422</v>
       </c>
@@ -11402,7 +11405,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="12" t="s">
         <v>422</v>
       </c>
@@ -11440,7 +11443,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
         <v>422</v>
       </c>
@@ -11478,7 +11481,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="12" t="s">
         <v>422</v>
       </c>
@@ -11516,7 +11519,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
         <v>422</v>
       </c>
@@ -11554,7 +11557,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="12" t="s">
         <v>422</v>
       </c>
@@ -11592,7 +11595,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
         <v>422</v>
       </c>
@@ -11630,7 +11633,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="12" t="s">
         <v>422</v>
       </c>
@@ -11668,7 +11671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
         <v>422</v>
       </c>
@@ -11706,7 +11709,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="12" t="s">
         <v>422</v>
       </c>
@@ -11744,7 +11747,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
         <v>422</v>
       </c>
@@ -11782,7 +11785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="12" t="s">
         <v>422</v>
       </c>
@@ -11820,7 +11823,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
         <v>422</v>
       </c>
@@ -11858,7 +11861,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="12" t="s">
         <v>422</v>
       </c>
@@ -11896,7 +11899,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
         <v>422</v>
       </c>
@@ -11934,7 +11937,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="12" t="s">
         <v>422</v>
       </c>
@@ -11972,7 +11975,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
         <v>422</v>
       </c>
@@ -12010,7 +12013,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="12" t="s">
         <v>422</v>
       </c>
@@ -12048,7 +12051,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
         <v>422</v>
       </c>
@@ -12086,7 +12089,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="12" t="s">
         <v>422</v>
       </c>
@@ -12124,7 +12127,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
         <v>422</v>
       </c>
@@ -12162,7 +12165,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="12" t="s">
         <v>422</v>
       </c>
@@ -12200,7 +12203,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
         <v>422</v>
       </c>
@@ -12238,7 +12241,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="12" t="s">
         <v>422</v>
       </c>
@@ -12276,7 +12279,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
         <v>422</v>
       </c>
@@ -12314,7 +12317,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="12" t="s">
         <v>422</v>
       </c>
@@ -12352,7 +12355,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
         <v>422</v>
       </c>
@@ -12390,7 +12393,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="12" t="s">
         <v>422</v>
       </c>
@@ -12428,7 +12431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
         <v>422</v>
       </c>
@@ -12466,7 +12469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="12" t="s">
         <v>422</v>
       </c>
@@ -12504,7 +12507,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
         <v>422</v>
       </c>
@@ -12542,7 +12545,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="12" t="s">
         <v>422</v>
       </c>
@@ -12580,7 +12583,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
         <v>422</v>
       </c>
@@ -12618,7 +12621,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="12" t="s">
         <v>422</v>
       </c>
@@ -12656,7 +12659,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
         <v>422</v>
       </c>
@@ -12694,7 +12697,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="12" t="s">
         <v>422</v>
       </c>
@@ -12732,7 +12735,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
         <v>422</v>
       </c>
@@ -12770,7 +12773,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="12" t="s">
         <v>422</v>
       </c>
@@ -12808,7 +12811,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
         <v>422</v>
       </c>
@@ -12846,7 +12849,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="12" t="s">
         <v>422</v>
       </c>
@@ -12884,7 +12887,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
         <v>422</v>
       </c>
@@ -12922,7 +12925,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
         <v>422</v>
       </c>
@@ -12960,7 +12963,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
         <v>422</v>
       </c>
@@ -12998,7 +13001,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="12" t="s">
         <v>422</v>
       </c>
@@ -13036,7 +13039,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
         <v>422</v>
       </c>
@@ -13074,7 +13077,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="12" t="s">
         <v>422</v>
       </c>
@@ -13112,7 +13115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
         <v>422</v>
       </c>
@@ -13150,7 +13153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="12" t="s">
         <v>422</v>
       </c>
@@ -13188,7 +13191,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
         <v>422</v>
       </c>
@@ -13226,7 +13229,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="12" t="s">
         <v>422</v>
       </c>
@@ -13264,7 +13267,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
         <v>422</v>
       </c>
@@ -13302,7 +13305,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="12" t="s">
         <v>422</v>
       </c>
@@ -13340,7 +13343,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
         <v>422</v>
       </c>
@@ -13378,7 +13381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="12" t="s">
         <v>422</v>
       </c>
@@ -13416,7 +13419,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
         <v>422</v>
       </c>
@@ -13454,7 +13457,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="12" t="s">
         <v>422</v>
       </c>
@@ -13492,7 +13495,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
         <v>422</v>
       </c>
@@ -13530,7 +13533,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="12" t="s">
         <v>422</v>
       </c>
@@ -13568,7 +13571,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
         <v>422</v>
       </c>
@@ -13606,7 +13609,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="12" t="s">
         <v>422</v>
       </c>
@@ -13644,7 +13647,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="8" t="s">
         <v>422</v>
       </c>
@@ -13682,7 +13685,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="12" t="s">
         <v>422</v>
       </c>
@@ -13720,7 +13723,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
         <v>422</v>
       </c>
@@ -13758,7 +13761,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="12" t="s">
         <v>422</v>
       </c>
@@ -13796,7 +13799,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="8" t="s">
         <v>422</v>
       </c>
@@ -13834,7 +13837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="12" t="s">
         <v>422</v>
       </c>
@@ -13872,7 +13875,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="8" t="s">
         <v>422</v>
       </c>
@@ -13910,7 +13913,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="12" t="s">
         <v>422</v>
       </c>
@@ -13948,7 +13951,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="8" t="s">
         <v>422</v>
       </c>
@@ -13986,7 +13989,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="12" t="s">
         <v>422</v>
       </c>
@@ -14024,7 +14027,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="8" t="s">
         <v>422</v>
       </c>
@@ -14062,7 +14065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="12" t="s">
         <v>422</v>
       </c>
@@ -14100,7 +14103,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
         <v>422</v>
       </c>
@@ -14138,7 +14141,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="12" t="s">
         <v>422</v>
       </c>
@@ -14176,7 +14179,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
         <v>422</v>
       </c>
@@ -14214,7 +14217,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="12" t="s">
         <v>422</v>
       </c>
@@ -14252,7 +14255,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="8" t="s">
         <v>422</v>
       </c>
@@ -14290,7 +14293,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="12" t="s">
         <v>422</v>
       </c>
@@ -14366,7 +14369,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="12" t="s">
         <v>422</v>
       </c>
@@ -14404,7 +14407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="8" t="s">
         <v>422</v>
       </c>
@@ -14476,11 +14479,11 @@
       <c r="K271" s="27">
         <v>46145</v>
       </c>
-      <c r="L271" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L271" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
         <v>422</v>
       </c>
@@ -14518,7 +14521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="12" t="s">
         <v>422</v>
       </c>
@@ -14556,7 +14559,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
         <v>422</v>
       </c>
@@ -14594,7 +14597,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="12" t="s">
         <v>422</v>
       </c>
@@ -14632,7 +14635,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
         <v>422</v>
       </c>
@@ -14670,7 +14673,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="12" t="s">
         <v>422</v>
       </c>
@@ -14708,7 +14711,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
         <v>422</v>
       </c>
@@ -14746,7 +14749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="12" t="s">
         <v>422</v>
       </c>
@@ -14784,7 +14787,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
         <v>422</v>
       </c>
@@ -14822,7 +14825,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="12" t="s">
         <v>422</v>
       </c>
@@ -14860,7 +14863,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
         <v>422</v>
       </c>
@@ -14898,7 +14901,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="12" t="s">
         <v>422</v>
       </c>
@@ -14936,7 +14939,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="8" t="s">
         <v>422</v>
       </c>
@@ -14974,7 +14977,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="12" t="s">
         <v>422</v>
       </c>
@@ -15012,7 +15015,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
         <v>422</v>
       </c>
@@ -15050,7 +15053,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="12" t="s">
         <v>422</v>
       </c>
@@ -15088,7 +15091,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="8" t="s">
         <v>422</v>
       </c>
@@ -15126,7 +15129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="12" t="s">
         <v>422</v>
       </c>
@@ -15164,7 +15167,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="8" t="s">
         <v>422</v>
       </c>
@@ -15202,7 +15205,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="12" t="s">
         <v>422</v>
       </c>
@@ -15240,7 +15243,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
         <v>422</v>
       </c>
@@ -15278,7 +15281,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="12" t="s">
         <v>422</v>
       </c>
@@ -15316,7 +15319,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="8" t="s">
         <v>422</v>
       </c>
@@ -15354,7 +15357,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="12" t="s">
         <v>422</v>
       </c>
@@ -15392,7 +15395,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="8" t="s">
         <v>422</v>
       </c>
@@ -15430,7 +15433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="12" t="s">
         <v>422</v>
       </c>
@@ -15468,7 +15471,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
         <v>422</v>
       </c>
@@ -15506,7 +15509,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="12" t="s">
         <v>422</v>
       </c>
@@ -15544,7 +15547,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="8" t="s">
         <v>422</v>
       </c>
@@ -15582,7 +15585,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="12" t="s">
         <v>422</v>
       </c>
@@ -15620,7 +15623,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="8" t="s">
         <v>422</v>
       </c>
@@ -15658,7 +15661,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="12" t="s">
         <v>422</v>
       </c>
@@ -15696,7 +15699,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
         <v>422</v>
       </c>
@@ -15734,7 +15737,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="12" t="s">
         <v>422</v>
       </c>
@@ -15772,7 +15775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="8" t="s">
         <v>422</v>
       </c>
@@ -15810,7 +15813,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="12" t="s">
         <v>422</v>
       </c>
@@ -15848,7 +15851,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="8" t="s">
         <v>422</v>
       </c>
@@ -15886,7 +15889,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="12" t="s">
         <v>422</v>
       </c>
@@ -15924,7 +15927,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="8" t="s">
         <v>422</v>
       </c>
@@ -15962,7 +15965,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="12" t="s">
         <v>422</v>
       </c>
@@ -16000,7 +16003,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="8" t="s">
         <v>422</v>
       </c>
@@ -16038,7 +16041,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="12" t="s">
         <v>422</v>
       </c>
@@ -16076,7 +16079,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="8" t="s">
         <v>422</v>
       </c>
@@ -16114,7 +16117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="12" t="s">
         <v>422</v>
       </c>
@@ -16152,7 +16155,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="8" t="s">
         <v>422</v>
       </c>
@@ -16190,7 +16193,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="12" t="s">
         <v>422</v>
       </c>
@@ -16228,7 +16231,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="8" t="s">
         <v>422</v>
       </c>
@@ -16266,7 +16269,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="12" t="s">
         <v>422</v>
       </c>
@@ -16304,7 +16307,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="8" t="s">
         <v>422</v>
       </c>
@@ -16342,7 +16345,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="12" t="s">
         <v>422</v>
       </c>
@@ -16418,7 +16421,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="12" t="s">
         <v>422</v>
       </c>
@@ -16456,7 +16459,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="8" t="s">
         <v>422</v>
       </c>
@@ -16494,7 +16497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="12" t="s">
         <v>422</v>
       </c>
@@ -16532,7 +16535,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="8" t="s">
         <v>422</v>
       </c>
@@ -16570,7 +16573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="12" t="s">
         <v>422</v>
       </c>
@@ -16608,7 +16611,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="8" t="s">
         <v>422</v>
       </c>
@@ -16646,7 +16649,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="12" t="s">
         <v>422</v>
       </c>
@@ -16684,7 +16687,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="8" t="s">
         <v>422</v>
       </c>
@@ -16722,7 +16725,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="12" t="s">
         <v>422</v>
       </c>
@@ -16760,7 +16763,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="8" t="s">
         <v>422</v>
       </c>
@@ -16798,7 +16801,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="12" t="s">
         <v>422</v>
       </c>
@@ -16836,7 +16839,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="8" t="s">
         <v>422</v>
       </c>
@@ -16874,7 +16877,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="12" t="s">
         <v>422</v>
       </c>
@@ -16912,7 +16915,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="8" t="s">
         <v>422</v>
       </c>
@@ -16950,7 +16953,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="12" t="s">
         <v>422</v>
       </c>
@@ -16988,7 +16991,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="8" t="s">
         <v>422</v>
       </c>
@@ -17026,7 +17029,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="12" t="s">
         <v>422</v>
       </c>
@@ -17064,7 +17067,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="8" t="s">
         <v>422</v>
       </c>
@@ -17102,7 +17105,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="12" t="s">
         <v>422</v>
       </c>
@@ -17140,7 +17143,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="8" t="s">
         <v>422</v>
       </c>
@@ -17178,7 +17181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="12" t="s">
         <v>422</v>
       </c>
@@ -17216,7 +17219,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="8" t="s">
         <v>422</v>
       </c>
@@ -17288,11 +17291,11 @@
       <c r="K345" s="24">
         <v>46148</v>
       </c>
-      <c r="L345" s="18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L345" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="8" t="s">
         <v>422</v>
       </c>
@@ -17330,7 +17333,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="12" t="s">
         <v>422</v>
       </c>
@@ -17368,7 +17371,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="8" t="s">
         <v>422</v>
       </c>
@@ -17406,7 +17409,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="12" t="s">
         <v>422</v>
       </c>
@@ -17444,7 +17447,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="8" t="s">
         <v>422</v>
       </c>
@@ -17482,7 +17485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="12" t="s">
         <v>422</v>
       </c>
@@ -17520,7 +17523,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="8" t="s">
         <v>422</v>
       </c>
@@ -17558,7 +17561,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="12" t="s">
         <v>422</v>
       </c>
@@ -17596,7 +17599,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="8" t="s">
         <v>422</v>
       </c>
@@ -17634,7 +17637,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="12" t="s">
         <v>422</v>
       </c>
@@ -17672,7 +17675,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="8" t="s">
         <v>422</v>
       </c>
@@ -17744,11 +17747,11 @@
       <c r="K357" s="24">
         <v>46143</v>
       </c>
-      <c r="L357" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L357" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="8" t="s">
         <v>422</v>
       </c>
@@ -17786,7 +17789,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="12" t="s">
         <v>422</v>
       </c>
@@ -17824,7 +17827,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="8" t="s">
         <v>422</v>
       </c>
@@ -17862,7 +17865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="12" t="s">
         <v>422</v>
       </c>
@@ -17900,7 +17903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="8" t="s">
         <v>422</v>
       </c>
@@ -17938,7 +17941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="12" t="s">
         <v>422</v>
       </c>
@@ -17976,7 +17979,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="8" t="s">
         <v>422</v>
       </c>
@@ -18014,7 +18017,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="12" t="s">
         <v>422</v>
       </c>
@@ -18052,7 +18055,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="8" t="s">
         <v>422</v>
       </c>
@@ -18090,7 +18093,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="12" t="s">
         <v>422</v>
       </c>
@@ -18128,7 +18131,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8" t="s">
         <v>422</v>
       </c>
@@ -18166,7 +18169,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="12" t="s">
         <v>422</v>
       </c>
@@ -18204,7 +18207,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="8" t="s">
         <v>422</v>
       </c>
@@ -18242,7 +18245,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="12" t="s">
         <v>422</v>
       </c>
@@ -18280,7 +18283,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="8" t="s">
         <v>422</v>
       </c>
@@ -18318,7 +18321,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="12" t="s">
         <v>422</v>
       </c>
@@ -18356,7 +18359,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="8" t="s">
         <v>422</v>
       </c>
@@ -18394,7 +18397,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="12" t="s">
         <v>422</v>
       </c>
@@ -18432,7 +18435,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="8" t="s">
         <v>422</v>
       </c>
@@ -18470,7 +18473,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="12" t="s">
         <v>422</v>
       </c>
@@ -18508,7 +18511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="8" t="s">
         <v>422</v>
       </c>
@@ -18546,7 +18549,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="12" t="s">
         <v>422</v>
       </c>
@@ -18584,7 +18587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="8" t="s">
         <v>422</v>
       </c>
@@ -18622,7 +18625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="12" t="s">
         <v>422</v>
       </c>
@@ -18660,7 +18663,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="8" t="s">
         <v>422</v>
       </c>
@@ -18698,7 +18701,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="12" t="s">
         <v>422</v>
       </c>
@@ -18736,7 +18739,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="8" t="s">
         <v>422</v>
       </c>
@@ -18808,11 +18811,11 @@
       <c r="K385" s="24">
         <v>46144</v>
       </c>
-      <c r="L385" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L385" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="8" t="s">
         <v>422</v>
       </c>
@@ -18850,7 +18853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="12" t="s">
         <v>422</v>
       </c>
@@ -18888,7 +18891,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="8" t="s">
         <v>422</v>
       </c>
@@ -18926,7 +18929,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="12" t="s">
         <v>422</v>
       </c>
@@ -18964,7 +18967,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="8" t="s">
         <v>422</v>
       </c>
@@ -19002,7 +19005,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="12" t="s">
         <v>422</v>
       </c>
@@ -19040,7 +19043,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="8" t="s">
         <v>422</v>
       </c>
@@ -19078,7 +19081,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="12" t="s">
         <v>422</v>
       </c>
@@ -19116,7 +19119,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="8" t="s">
         <v>422</v>
       </c>
@@ -19154,7 +19157,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="12" t="s">
         <v>422</v>
       </c>
@@ -19192,7 +19195,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="8" t="s">
         <v>422</v>
       </c>
@@ -19230,7 +19233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="12" t="s">
         <v>422</v>
       </c>
@@ -19268,7 +19271,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="8" t="s">
         <v>422</v>
       </c>
@@ -19306,7 +19309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="12" t="s">
         <v>422</v>
       </c>
@@ -19344,7 +19347,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="8" t="s">
         <v>422</v>
       </c>
@@ -19382,7 +19385,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="12" t="s">
         <v>422</v>
       </c>
@@ -19420,7 +19423,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="8" t="s">
         <v>422</v>
       </c>
@@ -19458,7 +19461,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="12" t="s">
         <v>422</v>
       </c>
@@ -19496,7 +19499,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="8" t="s">
         <v>422</v>
       </c>
@@ -19534,7 +19537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="12" t="s">
         <v>422</v>
       </c>
@@ -19572,7 +19575,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="8" t="s">
         <v>422</v>
       </c>
@@ -19610,7 +19613,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="12" t="s">
         <v>422</v>
       </c>
@@ -19648,7 +19651,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="8" t="s">
         <v>422</v>
       </c>
@@ -19686,7 +19689,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="12" t="s">
         <v>422</v>
       </c>
@@ -19724,7 +19727,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="8" t="s">
         <v>422</v>
       </c>
@@ -19762,7 +19765,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="12" t="s">
         <v>422</v>
       </c>
@@ -19800,7 +19803,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="8" t="s">
         <v>422</v>
       </c>
@@ -19838,7 +19841,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="12" t="s">
         <v>422</v>
       </c>
@@ -19876,7 +19879,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="8" t="s">
         <v>422</v>
       </c>
@@ -19914,7 +19917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="12" t="s">
         <v>422</v>
       </c>
@@ -19952,7 +19955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="8" t="s">
         <v>422</v>
       </c>
@@ -19990,7 +19993,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="417" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="12" t="s">
         <v>422</v>
       </c>
@@ -20028,7 +20031,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="418" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="8" t="s">
         <v>422</v>
       </c>
@@ -20066,7 +20069,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="12" t="s">
         <v>422</v>
       </c>
@@ -20104,7 +20107,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="8" t="s">
         <v>422</v>
       </c>
@@ -20142,7 +20145,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="12" t="s">
         <v>422</v>
       </c>
@@ -20215,10 +20218,10 @@
         <v>46149</v>
       </c>
       <c r="L422" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="423" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="12" t="s">
         <v>422</v>
       </c>
@@ -20256,7 +20259,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="8" t="s">
         <v>422</v>
       </c>
@@ -20294,7 +20297,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="12" t="s">
         <v>422</v>
       </c>
@@ -20332,7 +20335,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="8" t="s">
         <v>422</v>
       </c>
@@ -20370,7 +20373,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="12" t="s">
         <v>422</v>
       </c>
@@ -20408,7 +20411,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="8" t="s">
         <v>422</v>
       </c>
@@ -20446,7 +20449,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="429" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="12" t="s">
         <v>422</v>
       </c>
@@ -20484,7 +20487,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="8" t="s">
         <v>422</v>
       </c>
@@ -20522,7 +20525,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="12" t="s">
         <v>422</v>
       </c>
@@ -20560,7 +20563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="8" t="s">
         <v>422</v>
       </c>
@@ -20598,7 +20601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="12" t="s">
         <v>422</v>
       </c>
@@ -20636,7 +20639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="8" t="s">
         <v>422</v>
       </c>
@@ -20674,7 +20677,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="12" t="s">
         <v>422</v>
       </c>
@@ -20712,7 +20715,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="8" t="s">
         <v>422</v>
       </c>
@@ -20750,7 +20753,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="12" t="s">
         <v>422</v>
       </c>
@@ -20788,7 +20791,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="8" t="s">
         <v>422</v>
       </c>
@@ -20826,7 +20829,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="12" t="s">
         <v>422</v>
       </c>
@@ -20864,7 +20867,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="8" t="s">
         <v>422</v>
       </c>
@@ -20902,7 +20905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="12" t="s">
         <v>422</v>
       </c>
@@ -20940,7 +20943,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="8" t="s">
         <v>422</v>
       </c>
@@ -20978,7 +20981,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="12" t="s">
         <v>422</v>
       </c>
@@ -21016,7 +21019,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="8" t="s">
         <v>422</v>
       </c>
@@ -21054,7 +21057,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="12" t="s">
         <v>422</v>
       </c>
@@ -21092,7 +21095,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="8" t="s">
         <v>422</v>
       </c>
@@ -21130,7 +21133,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="12" t="s">
         <v>422</v>
       </c>
@@ -21168,7 +21171,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="8" t="s">
         <v>422</v>
       </c>
@@ -21206,7 +21209,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="12" t="s">
         <v>422</v>
       </c>
@@ -21244,7 +21247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="8" t="s">
         <v>422</v>
       </c>
@@ -21282,7 +21285,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="12" t="s">
         <v>422</v>
       </c>
@@ -21320,7 +21323,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="8" t="s">
         <v>422</v>
       </c>
@@ -21358,7 +21361,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="12" t="s">
         <v>422</v>
       </c>
@@ -21396,7 +21399,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="8" t="s">
         <v>422</v>
       </c>
@@ -21434,7 +21437,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="12" t="s">
         <v>422</v>
       </c>
@@ -21472,7 +21475,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="8" t="s">
         <v>422</v>
       </c>
@@ -21510,7 +21513,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="12" t="s">
         <v>422</v>
       </c>
@@ -21548,7 +21551,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="8" t="s">
         <v>422</v>
       </c>
@@ -21586,7 +21589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="12" t="s">
         <v>422</v>
       </c>
@@ -21624,7 +21627,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="8" t="s">
         <v>422</v>
       </c>
@@ -21662,7 +21665,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="12" t="s">
         <v>422</v>
       </c>
@@ -21700,7 +21703,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="8" t="s">
         <v>422</v>
       </c>
@@ -21738,7 +21741,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="12" t="s">
         <v>422</v>
       </c>
@@ -21776,7 +21779,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="8" t="s">
         <v>422</v>
       </c>
@@ -21814,7 +21817,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="12" t="s">
         <v>422</v>
       </c>
@@ -21852,7 +21855,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="8" t="s">
         <v>422</v>
       </c>
@@ -21890,7 +21893,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="12" t="s">
         <v>422</v>
       </c>
@@ -21928,7 +21931,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="8" t="s">
         <v>422</v>
       </c>
@@ -21966,7 +21969,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="12" t="s">
         <v>422</v>
       </c>
@@ -22004,7 +22007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="8" t="s">
         <v>422</v>
       </c>
@@ -22042,7 +22045,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="12" t="s">
         <v>422</v>
       </c>
@@ -22080,7 +22083,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="8" t="s">
         <v>422</v>
       </c>
@@ -22118,7 +22121,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="12" t="s">
         <v>422</v>
       </c>
@@ -22156,7 +22159,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="8" t="s">
         <v>422</v>
       </c>
@@ -22194,7 +22197,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="12" t="s">
         <v>422</v>
       </c>
@@ -22232,7 +22235,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="8" t="s">
         <v>422</v>
       </c>
@@ -22270,7 +22273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="12" t="s">
         <v>422</v>
       </c>
@@ -22308,7 +22311,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="8" t="s">
         <v>422</v>
       </c>
@@ -22346,7 +22349,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="12" t="s">
         <v>422</v>
       </c>
@@ -22384,7 +22387,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="8" t="s">
         <v>422</v>
       </c>
@@ -22422,7 +22425,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="12" t="s">
         <v>422</v>
       </c>
@@ -22460,7 +22463,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="8" t="s">
         <v>422</v>
       </c>
@@ -22498,7 +22501,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="12" t="s">
         <v>422</v>
       </c>
@@ -22536,7 +22539,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="8" t="s">
         <v>422</v>
       </c>
@@ -22574,7 +22577,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="485" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="12" t="s">
         <v>422</v>
       </c>
@@ -22612,7 +22615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="486" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="8" t="s">
         <v>422</v>
       </c>
@@ -22650,7 +22653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="12" t="s">
         <v>422</v>
       </c>
@@ -22688,7 +22691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="8" t="s">
         <v>422</v>
       </c>
@@ -22726,7 +22729,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="12" t="s">
         <v>422</v>
       </c>
@@ -22764,7 +22767,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="8" t="s">
         <v>422</v>
       </c>
@@ -22802,7 +22805,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="12" t="s">
         <v>422</v>
       </c>
@@ -22840,7 +22843,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="492" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="8" t="s">
         <v>422</v>
       </c>
@@ -22912,13 +22915,13 @@
       <c r="K493" s="31">
         <v>46145</v>
       </c>
-      <c r="L493" s="28" t="s">
-        <v>967</v>
+      <c r="L493" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494" s="28" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B494" s="28" t="s">
         <v>137</v>
@@ -22950,13 +22953,13 @@
       <c r="K494" s="31">
         <v>46147</v>
       </c>
-      <c r="L494" s="28" t="s">
-        <v>967</v>
+      <c r="L494" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495" s="28" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B495" s="28" t="s">
         <v>112</v>
@@ -22988,13 +22991,13 @@
       <c r="K495" s="31">
         <v>46149</v>
       </c>
-      <c r="L495" s="28" t="s">
-        <v>967</v>
+      <c r="L495" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496" s="28" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B496" s="28" t="s">
         <v>155</v>
@@ -23021,18 +23024,18 @@
         <v>3</v>
       </c>
       <c r="J496" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K496" s="31">
         <v>46152</v>
       </c>
-      <c r="L496" s="28" t="s">
-        <v>967</v>
+      <c r="L496" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A497" s="28" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B497" s="28" t="s">
         <v>42</v>
@@ -23064,16 +23067,16 @@
       <c r="K497" s="31">
         <v>46154</v>
       </c>
-      <c r="L497" s="28" t="s">
-        <v>967</v>
+      <c r="L497" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498" s="28" t="s">
+        <v>972</v>
+      </c>
+      <c r="B498" s="28" t="s">
         <v>973</v>
-      </c>
-      <c r="B498" s="28" t="s">
-        <v>974</v>
       </c>
       <c r="C498" s="29">
         <v>8051239876</v>
@@ -23094,7 +23097,7 @@
         <v>4</v>
       </c>
       <c r="I498" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J498" s="28" t="s">
         <v>98</v>
@@ -23102,13 +23105,13 @@
       <c r="K498" s="31">
         <v>46156</v>
       </c>
-      <c r="L498" s="28" t="s">
-        <v>967</v>
+      <c r="L498" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499" s="28" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B499" s="28" t="s">
         <v>131</v>
@@ -23135,18 +23138,18 @@
         <v>3</v>
       </c>
       <c r="J499" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K499" s="31">
         <v>46157</v>
       </c>
-      <c r="L499" s="28" t="s">
-        <v>967</v>
+      <c r="L499" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500" s="28" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B500" s="28" t="s">
         <v>126</v>
@@ -23170,7 +23173,7 @@
         <v>4</v>
       </c>
       <c r="I500" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J500" s="28" t="s">
         <v>21</v>
@@ -23178,13 +23181,13 @@
       <c r="K500" s="31">
         <v>46159</v>
       </c>
-      <c r="L500" s="28" t="s">
-        <v>967</v>
+      <c r="L500" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501" s="28" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B501" s="28" t="s">
         <v>254</v>
@@ -23216,13 +23219,13 @@
       <c r="K501" s="31">
         <v>46160</v>
       </c>
-      <c r="L501" s="28" t="s">
-        <v>20</v>
+      <c r="L501" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A502" s="28" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B502" s="28" t="s">
         <v>653</v>
@@ -23254,13 +23257,13 @@
       <c r="K502" s="31">
         <v>46161</v>
       </c>
-      <c r="L502" s="28" t="s">
+      <c r="L502" s="8" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503" s="28" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B503" s="28" t="s">
         <v>67</v>
@@ -23284,21 +23287,21 @@
         <v>4</v>
       </c>
       <c r="I503" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J503" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K503" s="31">
         <v>46162</v>
       </c>
-      <c r="L503" s="28" t="s">
+      <c r="L503" s="8" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504" s="28" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B504" s="28" t="s">
         <v>193</v>
@@ -23330,16 +23333,16 @@
       <c r="K504" s="31">
         <v>46163</v>
       </c>
-      <c r="L504" s="28" t="s">
-        <v>967</v>
+      <c r="L504" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505" s="28" t="s">
+        <v>981</v>
+      </c>
+      <c r="B505" s="28" t="s">
         <v>982</v>
-      </c>
-      <c r="B505" s="28" t="s">
-        <v>983</v>
       </c>
       <c r="C505" s="29">
         <v>8071234567</v>
@@ -23368,13 +23371,13 @@
       <c r="K505" s="31">
         <v>46164</v>
       </c>
-      <c r="L505" s="28" t="s">
-        <v>20</v>
+      <c r="L505" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506" s="28" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B506" s="28" t="s">
         <v>106</v>
@@ -23398,7 +23401,7 @@
         <v>4</v>
       </c>
       <c r="I506" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J506" s="28" t="s">
         <v>22</v>
@@ -23406,16 +23409,16 @@
       <c r="K506" s="31">
         <v>46165</v>
       </c>
-      <c r="L506" s="28" t="s">
-        <v>967</v>
+      <c r="L506" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A507" s="28" t="s">
+        <v>984</v>
+      </c>
+      <c r="B507" s="28" t="s">
         <v>985</v>
-      </c>
-      <c r="B507" s="28" t="s">
-        <v>986</v>
       </c>
       <c r="C507" s="29">
         <v>8091234589</v>
@@ -23439,18 +23442,18 @@
         <v>3</v>
       </c>
       <c r="J507" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K507" s="31">
         <v>46166</v>
       </c>
-      <c r="L507" s="28" t="s">
-        <v>20</v>
+      <c r="L507" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508" s="28" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B508" s="28" t="s">
         <v>152</v>
@@ -23482,13 +23485,13 @@
       <c r="K508" s="31">
         <v>46167</v>
       </c>
-      <c r="L508" s="28" t="s">
-        <v>967</v>
+      <c r="L508" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509" s="28" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B509" s="28" t="s">
         <v>709</v>
@@ -23520,13 +23523,13 @@
       <c r="K509" s="31">
         <v>46168</v>
       </c>
-      <c r="L509" s="28" t="s">
-        <v>20</v>
+      <c r="L509" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510" s="28" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B510" s="28" t="s">
         <v>118</v>
@@ -23550,7 +23553,7 @@
         <v>4</v>
       </c>
       <c r="I510" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J510" s="28" t="s">
         <v>22</v>
@@ -23558,13 +23561,13 @@
       <c r="K510" s="31">
         <v>46169</v>
       </c>
-      <c r="L510" s="28" t="s">
-        <v>967</v>
+      <c r="L510" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A511" s="28" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B511" s="28" t="s">
         <v>158</v>
@@ -23591,18 +23594,18 @@
         <v>3</v>
       </c>
       <c r="J511" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K511" s="31">
         <v>46170</v>
       </c>
-      <c r="L511" s="28" t="s">
-        <v>20</v>
+      <c r="L511" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A512" s="28" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B512" s="28" t="s">
         <v>316</v>
@@ -23634,16 +23637,16 @@
       <c r="K512" s="31">
         <v>46171</v>
       </c>
-      <c r="L512" s="28" t="s">
-        <v>967</v>
+      <c r="L512" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A513" s="28" t="s">
+        <v>991</v>
+      </c>
+      <c r="B513" s="28" t="s">
         <v>992</v>
-      </c>
-      <c r="B513" s="28" t="s">
-        <v>993</v>
       </c>
       <c r="C513" s="29">
         <v>8091234590</v>
@@ -23664,7 +23667,7 @@
         <v>4</v>
       </c>
       <c r="I513" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J513" s="28" t="s">
         <v>21</v>
@@ -23672,13 +23675,13 @@
       <c r="K513" s="31">
         <v>46143</v>
       </c>
-      <c r="L513" s="28" t="s">
-        <v>967</v>
+      <c r="L513" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A514" s="28" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B514" s="28" t="s">
         <v>146</v>
@@ -23710,13 +23713,13 @@
       <c r="K514" s="31">
         <v>46144</v>
       </c>
-      <c r="L514" s="28" t="s">
-        <v>967</v>
+      <c r="L514" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A515" s="28" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B515" s="28" t="s">
         <v>210</v>
@@ -23743,18 +23746,18 @@
         <v>3</v>
       </c>
       <c r="J515" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K515" s="31">
         <v>46146</v>
       </c>
-      <c r="L515" s="28" t="s">
-        <v>967</v>
+      <c r="L515" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A516" s="28" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B516" s="28" t="s">
         <v>325</v>
@@ -23778,7 +23781,7 @@
         <v>4</v>
       </c>
       <c r="I516" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J516" s="28" t="s">
         <v>98</v>
@@ -23786,13 +23789,13 @@
       <c r="K516" s="31">
         <v>46148</v>
       </c>
-      <c r="L516" s="28" t="s">
-        <v>967</v>
+      <c r="L516" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A517" s="28" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B517" s="28" t="s">
         <v>103</v>
@@ -23824,13 +23827,13 @@
       <c r="K517" s="31">
         <v>46150</v>
       </c>
-      <c r="L517" s="28" t="s">
-        <v>967</v>
+      <c r="L517" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A518" s="28" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B518" s="28" t="s">
         <v>96</v>
@@ -23862,16 +23865,16 @@
       <c r="K518" s="31">
         <v>46151</v>
       </c>
-      <c r="L518" s="28" t="s">
-        <v>967</v>
+      <c r="L518" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A519" s="28" t="s">
+        <v>998</v>
+      </c>
+      <c r="B519" s="28" t="s">
         <v>999</v>
-      </c>
-      <c r="B519" s="28" t="s">
-        <v>1000</v>
       </c>
       <c r="C519" s="29">
         <v>8061234501</v>
@@ -23892,24 +23895,24 @@
         <v>4</v>
       </c>
       <c r="I519" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J519" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K519" s="31">
         <v>46153</v>
       </c>
-      <c r="L519" s="28" t="s">
-        <v>967</v>
+      <c r="L519" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A520" s="28" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B520" s="28" t="s">
         <v>1001</v>
-      </c>
-      <c r="B520" s="28" t="s">
-        <v>1002</v>
       </c>
       <c r="C520" s="29">
         <v>8051234545</v>
@@ -23938,13 +23941,13 @@
       <c r="K520" s="31">
         <v>46155</v>
       </c>
-      <c r="L520" s="28" t="s">
-        <v>967</v>
+      <c r="L520" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="521" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A521" s="28" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B521" s="28" t="s">
         <v>228</v>
@@ -23968,7 +23971,7 @@
         <v>4</v>
       </c>
       <c r="I521" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J521" s="28" t="s">
         <v>21</v>
@@ -23976,16 +23979,16 @@
       <c r="K521" s="31">
         <v>46158</v>
       </c>
-      <c r="L521" s="28" t="s">
-        <v>20</v>
+      <c r="L521" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="522" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A522" s="28" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B522" s="28" t="s">
         <v>1004</v>
-      </c>
-      <c r="B522" s="28" t="s">
-        <v>1005</v>
       </c>
       <c r="C522" s="29">
         <v>8031234567</v>
@@ -24014,13 +24017,13 @@
       <c r="K522" s="31">
         <v>46172</v>
       </c>
-      <c r="L522" s="28" t="s">
-        <v>967</v>
+      <c r="L522" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A523" s="28" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B523" s="28" t="s">
         <v>100</v>
@@ -24047,21 +24050,21 @@
         <v>3</v>
       </c>
       <c r="J523" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K523" s="31">
         <v>46173</v>
       </c>
-      <c r="L523" s="28" t="s">
-        <v>967</v>
+      <c r="L523" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A524" s="28" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B524" s="28" t="s">
         <v>1007</v>
-      </c>
-      <c r="B524" s="28" t="s">
-        <v>1008</v>
       </c>
       <c r="C524" s="29">
         <v>8051234578</v>
@@ -24082,7 +24085,7 @@
         <v>4</v>
       </c>
       <c r="I524" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J524" s="28" t="s">
         <v>98</v>
@@ -24090,13 +24093,13 @@
       <c r="K524" s="31">
         <v>46145</v>
       </c>
-      <c r="L524" s="28" t="s">
-        <v>967</v>
+      <c r="L524" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A525" s="28" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B525" s="28" t="s">
         <v>367</v>
@@ -24128,16 +24131,16 @@
       <c r="K525" s="31">
         <v>46147</v>
       </c>
-      <c r="L525" s="28" t="s">
-        <v>967</v>
+      <c r="L525" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="526" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A526" s="28" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B526" s="28" t="s">
         <v>1010</v>
-      </c>
-      <c r="B526" s="28" t="s">
-        <v>1011</v>
       </c>
       <c r="C526" s="29">
         <v>8061234567</v>
@@ -24166,13 +24169,13 @@
       <c r="K526" s="31">
         <v>46149</v>
       </c>
-      <c r="L526" s="28" t="s">
-        <v>967</v>
+      <c r="L526" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="527" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A527" s="28" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B527" s="28" t="s">
         <v>115</v>
@@ -24196,21 +24199,21 @@
         <v>4</v>
       </c>
       <c r="I527" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J527" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K527" s="31">
         <v>46152</v>
       </c>
-      <c r="L527" s="28" t="s">
-        <v>967</v>
+      <c r="L527" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A528" s="28" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B528" s="28" t="s">
         <v>176</v>
@@ -24242,13 +24245,13 @@
       <c r="K528" s="31">
         <v>46154</v>
       </c>
-      <c r="L528" s="28" t="s">
-        <v>967</v>
+      <c r="L528" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A529" s="28" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B529" s="28" t="s">
         <v>61</v>
@@ -24272,7 +24275,7 @@
         <v>4</v>
       </c>
       <c r="I529" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J529" s="28" t="s">
         <v>21</v>
@@ -24280,13 +24283,13 @@
       <c r="K529" s="31">
         <v>46156</v>
       </c>
-      <c r="L529" s="28" t="s">
-        <v>967</v>
+      <c r="L529" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A530" s="28" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B530" s="28" t="s">
         <v>225</v>
@@ -24318,13 +24321,13 @@
       <c r="K530" s="31">
         <v>46157</v>
       </c>
-      <c r="L530" s="28" t="s">
-        <v>967</v>
+      <c r="L530" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="531" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A531" s="28" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B531" s="28" t="s">
         <v>364</v>
@@ -24348,24 +24351,24 @@
         <v>4</v>
       </c>
       <c r="I531" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J531" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K531" s="31">
         <v>46159</v>
       </c>
-      <c r="L531" s="28" t="s">
-        <v>967</v>
+      <c r="L531" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A532" s="28" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B532" s="28" t="s">
         <v>1017</v>
-      </c>
-      <c r="B532" s="28" t="s">
-        <v>1018</v>
       </c>
       <c r="C532" s="29">
         <v>8061234534</v>
@@ -24394,13 +24397,13 @@
       <c r="K532" s="31">
         <v>46160</v>
       </c>
-      <c r="L532" s="28" t="s">
-        <v>967</v>
+      <c r="L532" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A533" s="28" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B533" s="28" t="s">
         <v>184</v>
@@ -24432,16 +24435,16 @@
       <c r="K533" s="31">
         <v>46161</v>
       </c>
-      <c r="L533" s="28" t="s">
-        <v>967</v>
+      <c r="L533" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A534" s="28" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B534" s="28" t="s">
         <v>1020</v>
-      </c>
-      <c r="B534" s="28" t="s">
-        <v>1021</v>
       </c>
       <c r="C534" s="29">
         <v>8051234512</v>
@@ -24462,7 +24465,7 @@
         <v>4</v>
       </c>
       <c r="I534" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J534" s="28" t="s">
         <v>22</v>
@@ -24470,13 +24473,13 @@
       <c r="K534" s="31">
         <v>46162</v>
       </c>
-      <c r="L534" s="28" t="s">
-        <v>967</v>
+      <c r="L534" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A535" s="28" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B535" s="28" t="s">
         <v>289</v>
@@ -24503,18 +24506,18 @@
         <v>3</v>
       </c>
       <c r="J535" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K535" s="31">
         <v>46163</v>
       </c>
-      <c r="L535" s="28" t="s">
-        <v>20</v>
+      <c r="L535" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A536" s="28" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B536" s="28" t="s">
         <v>373</v>
@@ -24546,16 +24549,16 @@
       <c r="K536" s="31">
         <v>46164</v>
       </c>
-      <c r="L536" s="28" t="s">
-        <v>20</v>
+      <c r="L536" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A537" s="28" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B537" s="28" t="s">
         <v>1024</v>
-      </c>
-      <c r="B537" s="28" t="s">
-        <v>1025</v>
       </c>
       <c r="C537" s="29">
         <v>8091234590</v>
@@ -24576,7 +24579,7 @@
         <v>4</v>
       </c>
       <c r="I537" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J537" s="28" t="s">
         <v>21</v>
@@ -24584,13 +24587,13 @@
       <c r="K537" s="31">
         <v>46165</v>
       </c>
-      <c r="L537" s="28" t="s">
-        <v>967</v>
+      <c r="L537" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A538" s="28" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B538" s="28" t="s">
         <v>204</v>
@@ -24622,13 +24625,13 @@
       <c r="K538" s="31">
         <v>46166</v>
       </c>
-      <c r="L538" s="28" t="s">
-        <v>967</v>
+      <c r="L538" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A539" s="28" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B539" s="28" t="s">
         <v>201</v>
@@ -24652,21 +24655,21 @@
         <v>4</v>
       </c>
       <c r="I539" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J539" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K539" s="31">
         <v>46167</v>
       </c>
-      <c r="L539" s="28" t="s">
-        <v>967</v>
+      <c r="L539" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A540" s="28" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B540" s="28" t="s">
         <v>581</v>
@@ -24698,16 +24701,16 @@
       <c r="K540" s="31">
         <v>46168</v>
       </c>
-      <c r="L540" s="28" t="s">
-        <v>967</v>
+      <c r="L540" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A541" s="28" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B541" s="28" t="s">
         <v>1029</v>
-      </c>
-      <c r="B541" s="28" t="s">
-        <v>1030</v>
       </c>
       <c r="C541" s="29">
         <v>7031234567</v>
@@ -24728,7 +24731,7 @@
         <v>4</v>
       </c>
       <c r="I541" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J541" s="28" t="s">
         <v>21</v>
@@ -24736,13 +24739,13 @@
       <c r="K541" s="31">
         <v>46169</v>
       </c>
-      <c r="L541" s="28" t="s">
-        <v>967</v>
+      <c r="L541" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="542" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A542" s="28" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B542" s="28" t="s">
         <v>461</v>
@@ -24774,16 +24777,16 @@
       <c r="K542" s="31">
         <v>46170</v>
       </c>
-      <c r="L542" s="28" t="s">
-        <v>20</v>
+      <c r="L542" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A543" s="28" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B543" s="28" t="s">
         <v>1032</v>
-      </c>
-      <c r="B543" s="28" t="s">
-        <v>1033</v>
       </c>
       <c r="C543" s="29">
         <v>8031234512</v>
@@ -24804,24 +24807,24 @@
         <v>4</v>
       </c>
       <c r="I543" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J543" s="28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="K543" s="31">
         <v>46171</v>
       </c>
-      <c r="L543" s="28" t="s">
-        <v>967</v>
+      <c r="L543" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A544" s="28" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B544" s="28" t="s">
         <v>1034</v>
-      </c>
-      <c r="B544" s="28" t="s">
-        <v>1035</v>
       </c>
       <c r="C544" s="29">
         <v>8051234556</v>
@@ -24850,13 +24853,13 @@
       <c r="K544" s="31">
         <v>46172</v>
       </c>
-      <c r="L544" s="28" t="s">
-        <v>967</v>
+      <c r="L544" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A545" s="28" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B545" s="28" t="s">
         <v>313</v>
@@ -24888,13 +24891,13 @@
       <c r="K545" s="31">
         <v>46173</v>
       </c>
-      <c r="L545" s="28" t="s">
-        <v>967</v>
+      <c r="L545" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A546" s="28" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B546" s="28" t="s">
         <v>234</v>
@@ -24918,7 +24921,7 @@
         <v>4</v>
       </c>
       <c r="I546" s="28" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J546" s="28" t="s">
         <v>22</v>
@@ -24926,11 +24929,11 @@
       <c r="K546" s="31">
         <v>46143</v>
       </c>
-      <c r="L546" s="28" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L546" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="547" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="12" t="s">
         <v>422</v>
       </c>
